--- a/.yuleosh/reports/layer1-report.xlsx
+++ b/.yuleosh/reports/layer1-report.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>No MISRA violations</t>
+          <t>1 MISRA violation(s) (0 required, 0 advisory) — see .yuleosh/reports/misra-report.json</t>
         </is>
       </c>
     </row>
